--- a/HW1_detection_matrix.xlsx
+++ b/HW1_detection_matrix.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Matrix" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Table1" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Table2" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Rules &amp; flags" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Explanations" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Rules &amp; flags" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Matrix!$A$1:$M$46</definedName>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="137">
   <si>
     <t xml:space="preserve">Smell</t>
   </si>
@@ -298,12 +299,27 @@
     <t xml:space="preserve">PMD vs ChatGPT (Run 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">(to write)</t>
+    <t xml:space="preserve">Missed Parser.parse and TextHelpAppendable.adjustTableFormat; added printUsage (NCSS 18) and parsePattern (NCSS 28), both under PMD's threshold of 30.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagged only HelpFormatter. PMD-only: CommandLine, DefaultParser, Option, Parser.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagged only the 6-, 8- and 9-parameter printHelp overloads. PMD also flags seven 5-parameter methods, none reported.</t>
   </si>
   <si>
     <t xml:space="preserve">PMD vs DeepSeek (Run 1)</t>
   </si>
   <si>
+    <t xml:space="preserve">Missed only TextStyle.pad; added 5 methods below PMD's threshold (printHelp 9-param NCSS 12, printUsage 18, findWrapPos 17, DefaultParser.parse 16, parsePattern 28).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matched 4 of 5; missed Parser; added TextHelpAppendable, which PMD did not flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matched 5 of 10 (all printHelp overloads and appendOptions). Added 3- and 4-parameter methods (Options.addOption, Option ctor, DefaultParser.parse); missed printOptions, renderOptions and both AbstractHelpFormatter methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LLM</t>
   </si>
   <si>
@@ -328,12 +344,75 @@
     <t xml:space="preserve">ChatGPT</t>
   </si>
   <si>
-    <t xml:space="preserve">(pending scoring)</t>
-  </si>
-  <si>
     <t xml:space="preserve">DeepSeek</t>
   </si>
   <si>
+    <t xml:space="preserve">Detection # (Run 1, source order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Code reference (0/1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smell characteristic (0/1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence-to-smell link (0/1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score (/3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rationale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cites handleOption(), handleLongOptionWithoutEqual(), handleConcatenatedOptions(), currentOption.processValue(); says length plus many token-parsing cases make control flow hard to follow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GnuParser.flatten(Options, String[], boolean)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cites eatTheRest, indexOfEqual(), options.hasOption(); says it combines traversal, recognition and splitting, so is more complex than a single operation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lists printHelp/printUsage/findWrapPos, fields defaultWidth/optionComparator; says formatting, layout, wrapping and output are combined in one large class.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpFormatter.printHelp(int, String, String, Options, String, boolean)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names all six parameters; says six separate inputs exceed a comfortable signature size.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpFormatter.printHelp(PrintWriter, int, String, String, Options, int, int, String)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names all eight parameters; says independent arguments make the signature cumbersome to call correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quotes the actual conditions (token.length() == 1, pos == -1, isJavaProperty...); says many alternative token shapes make the flow long and hard to follow.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DefaultParser.parse(Options, Properties, NonOptionAction, String...)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quotes expectedOpts, setSelected(null), handleToken, checkRequiredArgs; says setup, dispatch, reset, properties and validation are bundled in one body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lists getParsedOptionValue overloads, resolveOption, handleDeprecated; says it covers storage, lookup, typed parsing, properties and iteration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lists fields (cmd, currentOption, skipParsing) and helpers; says it owns classification, matching, bookkeeping, properties and CommandLine construction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names the four parameters, but only says the signature "carries several unrelated concerns"; never says the list is long or hard to call, so no smell characteristic and no link.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpFormatter.appendOptions(A, int, Options, int, int)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names the five parameters; says they are passed positionally and make the call hard to interpret.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Matching rules used (state these in the report)</t>
   </si>
   <si>
@@ -358,18 +437,19 @@
     <t xml:space="preserve">7. Distinct detections per LLM = union of units across its 3 runs; consistency = detections found in all 3 runs / distinct detections.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blank cells in Table1 Comments and Table2 explanation quality are filled later.</t>
+    <t xml:space="preserve">Explanations sheet: scored draft (Claude); the student should review. ChatGPT God Class has one Run 1 detection, so one explanation; 11 explanations in total.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0;\-0;;@"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -485,7 +565,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -516,6 +596,18 @@
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2854,7 +2946,7 @@
         <v>0.2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2889,12 +2981,12 @@
         <v>0.3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
@@ -2924,12 +3016,12 @@
         <v>0.5</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>45</v>
@@ -2959,12 +3051,12 @@
         <v>0.666666666666667</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>57</v>
@@ -2994,7 +3086,7 @@
         <v>0.333333333333333</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3028,33 +3120,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>13</v>
@@ -3079,13 +3171,14 @@
         <f aca="false">IF(F2=0,0,E2/F2)</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>100</v>
+      <c r="H2" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A2,Explanations!$B$2:$B$12,B2),"n/a")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>45</v>
@@ -3110,13 +3203,14 @@
         <f aca="false">IF(F3=0,0,E3/F3)</f>
         <v>1</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>100</v>
+      <c r="H3" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A3,Explanations!$B$2:$B$12,B3),"n/a")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>57</v>
@@ -3141,13 +3235,14 @@
         <f aca="false">IF(F4=0,0,E4/F4)</f>
         <v>0.125</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>100</v>
+      <c r="H4" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A4,Explanations!$B$2:$B$12,B4),"n/a")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
@@ -3172,13 +3267,14 @@
         <f aca="false">IF(F5=0,0,E5/F5)</f>
         <v>0.214285714285714</v>
       </c>
-      <c r="H5" s="6" t="s">
-        <v>100</v>
+      <c r="H5" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A5,Explanations!$B$2:$B$12,B5),"n/a")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>45</v>
@@ -3203,13 +3299,14 @@
         <f aca="false">IF(F6=0,0,E6/F6)</f>
         <v>0.625</v>
       </c>
-      <c r="H6" s="6" t="s">
-        <v>100</v>
+      <c r="H6" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A6,Explanations!$B$2:$B$12,B6),"n/a")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>57</v>
@@ -3234,8 +3331,9 @@
         <f aca="false">IF(F7=0,0,E7/F7)</f>
         <v>0.285714285714286</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>100</v>
+      <c r="H7" s="8" t="n">
+        <f aca="false">IFERROR(AVERAGEIFS(Explanations!$H$2:$H$12,Explanations!$A$2:$A$12,A7,Explanations!$B$2:$B$12,B7),"n/a")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3254,6 +3352,393 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="90"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <f aca="false">SUM(E2:G2)</f>
+        <v>3</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <f aca="false">SUM(E3:G3)</f>
+        <v>3</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <f aca="false">SUM(E4:G4)</f>
+        <v>3</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <f aca="false">SUM(E5:G5)</f>
+        <v>3</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <f aca="false">SUM(E6:G6)</f>
+        <v>3</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <f aca="false">SUM(E7:G7)</f>
+        <v>3</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <f aca="false">SUM(E8:G8)</f>
+        <v>3</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <f aca="false">SUM(E9:G9)</f>
+        <v>3</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <f aca="false">SUM(E10:G10)</f>
+        <v>3</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <f aca="false">SUM(E11:G11)</f>
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <f aca="false">SUM(E12:G12)</f>
+        <v>3</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -3261,48 +3746,48 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>102</v>
+      <c r="A1" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>103</v>
+      <c r="A2" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>104</v>
+      <c r="A3" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>105</v>
+      <c r="A4" s="12" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>106</v>
+      <c r="A5" s="12" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>107</v>
+      <c r="A6" s="12" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>108</v>
+      <c r="A7" s="12" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>109</v>
+      <c r="A8" s="12" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>110</v>
+      <c r="A9" s="12" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
